--- a/Result/profitability/2406.xlsx
+++ b/Result/profitability/2406.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.17875</v>
+        <v>-0.14375</v>
       </c>
       <c r="N2" t="n">
-        <v>8.754999999999999</v>
+        <v>9.55125</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>-0.16</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.17125</v>
+        <v>-0.09250000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>9.647499999999999</v>
+        <v>11.22875</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -901,13 +901,13 @@
         <v>-0.09</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.11125</v>
+        <v>-0.08000000000000002</v>
       </c>
       <c r="N4" t="n">
-        <v>11.1925</v>
+        <v>11.6975</v>
       </c>
       <c r="O4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
         <v>1</v>
@@ -919,7 +919,7 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -1020,10 +1020,10 @@
         <v>-0.28</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1225</v>
+        <v>-0.04375000000000003</v>
       </c>
       <c r="N5" t="n">
-        <v>11.95375</v>
+        <v>12.58375</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1139,10 +1139,10 @@
         <v>0.09</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.04000000000000002</v>
+        <v>-0.01375000000000003</v>
       </c>
       <c r="N6" t="n">
-        <v>13.88875</v>
+        <v>13.73375</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1268,10 +1268,10 @@
         <v>0.22</v>
       </c>
       <c r="M7" t="n">
-        <v>0.006249999999999981</v>
+        <v>0.01374999999999997</v>
       </c>
       <c r="N7" t="n">
-        <v>15.3875</v>
+        <v>15.385</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1395,10 +1395,10 @@
         <v>1.31</v>
       </c>
       <c r="M8" t="n">
-        <v>0.17</v>
+        <v>0.14375</v>
       </c>
       <c r="N8" t="n">
-        <v>17.1875</v>
+        <v>16.19625</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -2030,7 +2030,7 @@
         <v>0.89</v>
       </c>
       <c r="M13" t="n">
-        <v>0.6175</v>
+        <v>0.6174999999999999</v>
       </c>
       <c r="N13" t="n">
         <v>28.61875</v>
@@ -9832,6 +9832,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2406</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>2826</v>
+      </c>
+      <c r="D75" t="n">
+        <v>2508</v>
+      </c>
+      <c r="E75" t="n">
+        <v>318</v>
+      </c>
+      <c r="F75" t="n">
+        <v>11.26</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-7</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-0.24%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>106</v>
+      </c>
+      <c r="J75" t="n">
+        <v>99</v>
+      </c>
+      <c r="K75" t="n">
+        <v>21</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.17125</v>
+      </c>
+      <c r="N75" t="n">
+        <v>8.89625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.21</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.7777777777777778</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-7.930000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.4132360604481501</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.6299999999999999</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.105263157894737</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.8102893890675242</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
